--- a/data/xlsx/pksf--it-freelancing.xlsx
+++ b/data/xlsx/pksf--it-freelancing.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -503,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -576,9 +588,9 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Classroom – 350 sft (33 sqm)
-Workshop/ lab – 800 sft (75 sqm)
-                     OR
-Classroom cum workshop – 1000 sft (93 sqm)</t>
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -643,7 +655,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -667,7 +679,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -691,7 +703,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -715,7 +727,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -740,7 +752,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -765,13 +777,13 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Tools: 
-Office application, photo editing software and video editing software</t>
+Office application, photo editing software and video editing software, SEO Tools, Social Media Management, Email Marketing, Content Creation, CRM, Data Entry, Affiliate Marketing, bid for job</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -790,7 +802,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -814,12 +826,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Internet connectivity with power back-up</t>
+          <t>Internet connectivity (Minimum 10 Mbps) with power back-up (at least 01 hour)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -838,7 +850,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -846,18 +858,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="15">
+      <c r="E24" s="19">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="19">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -866,7 +878,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="15">
+      <c r="F25" s="19">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -874,7 +886,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -883,18 +895,25 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="15">
+      <c r="F27" s="19">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
@@ -903,6 +922,7 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/xlsx/pksf--it-freelancing.xlsx
+++ b/data/xlsx/pksf--it-freelancing.xlsx
@@ -733,7 +733,7 @@
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel Core i5 processor (8th Gen), 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">

--- a/data/xlsx/pksf--it-freelancing.xlsx
+++ b/data/xlsx/pksf--it-freelancing.xlsx
@@ -733,7 +733,7 @@
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
